--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484207_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484207_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9191</v>
+        <v>5.9875</v>
       </c>
       <c r="E2" t="n">
-        <v>3.219</v>
+        <v>3.1784</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7001</v>
+        <v>2.809</v>
       </c>
       <c r="G2" t="n">
         <v>2.8793</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2585</v>
+        <v>1.3268</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6824</v>
+        <v>0.6419</v>
       </c>
       <c r="U2" t="n">
-        <v>0.576</v>
+        <v>0.6849</v>
       </c>
       <c r="V2" t="n">
         <v>0.6093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.416</v>
+        <v>4.821</v>
       </c>
       <c r="E3" t="n">
-        <v>2.802</v>
+        <v>3.1253</v>
       </c>
       <c r="F3" t="n">
-        <v>1.614</v>
+        <v>1.6957</v>
       </c>
       <c r="G3" t="n">
         <v>2.2757</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6129</v>
+        <v>1.0179</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1294</v>
+        <v>0.4527</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4836</v>
+        <v>0.5653</v>
       </c>
       <c r="V3" t="n">
         <v>0.9414</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4093</v>
+        <v>4.2225</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1061</v>
+        <v>0.925</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5154</v>
+        <v>3.2975</v>
       </c>
       <c r="G4" t="n">
         <v>1.7719</v>
@@ -766,13 +766,13 @@
         <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2701</v>
+        <v>1.0833</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.2443</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0569</v>
+        <v>0.839</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6686</v>
+        <v>1.5754</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8125</v>
+        <v>-0.2059</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8561</v>
+        <v>1.7813</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09089999999999999</v>
+        <v>2.6212</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1681</v>
+        <v>3.0663</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0772</v>
+        <v>-0.4451</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4314</v>
+        <v>2.6363</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0246</v>
+        <v>2.5416</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3405</v>
+        <v>-0.0152</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1435</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.484</v>
+        <v>-0.5399</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1721</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>-4.8836</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9766</v>
+        <v>1.4471</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5381</v>
+        <v>0.8227</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4385</v>
+        <v>0.6244</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7731</v>
+        <v>1.2186</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7731</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1856</v>
+        <v>1.4279</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0775</v>
+        <v>-0.4009</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1081</v>
+        <v>1.8289</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6212</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0663</v>
+        <v>2.1681</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4451</v>
+        <v>-2.0772</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6363</v>
+        <v>0.4314</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5416</v>
+        <v>1.0246</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09470000000000001</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0152</v>
+        <v>-0.3405</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5247000000000001</v>
+        <v>1.1435</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5399</v>
+        <v>-1.484</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.7115</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8836</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0574</v>
+        <v>0.736</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1061</v>
+        <v>0.3247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9512</v>
+        <v>0.4112</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2186</v>
+        <v>1.7731</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>1.7731</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4028</v>
+        <v>1.0173</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9174</v>
+        <v>1.423</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.4057</v>
       </c>
       <c r="G7" t="n">
         <v>1.8475</v>
@@ -1000,13 +1000,13 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4996</v>
+        <v>0.1149</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3631</v>
+        <v>0.1424</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1365</v>
+        <v>-0.0275</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5545</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3965</v>
+        <v>0.801</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8804</v>
+        <v>1.2848</v>
       </c>
       <c r="F8" t="n">
         <v>-0.4838</v>
@@ -1078,10 +1078,10 @@
         <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2091</v>
+        <v>0.1953</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3631</v>
+        <v>0.0413</v>
       </c>
       <c r="U8" t="n">
         <v>0.154</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1328</v>
+        <v>-0.0259</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1768</v>
+        <v>1.9801</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3097</v>
+        <v>-2.0061</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4767</v>
+        <v>0.6019</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8565</v>
+        <v>0.7235</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6202</v>
+        <v>-0.1216</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5611</v>
+        <v>2.0399</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4802</v>
+        <v>1.352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0809</v>
+        <v>0.6879</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0844</v>
+        <v>-1.438</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6237</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5393</v>
+        <v>-0.8095</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1831</v>
+        <v>-0.1905</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9245</v>
+        <v>-0.0598</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2586</v>
+        <v>-0.1308</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.988</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.6559</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6349</v>
+        <v>-0.5634</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6163</v>
+        <v>-1.5866</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2512</v>
+        <v>1.0232</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6019</v>
+        <v>-2.2377</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7235</v>
+        <v>-0.6068</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1216</v>
+        <v>-1.6309</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0399</v>
+        <v>-1.2689</v>
       </c>
       <c r="K10" t="n">
-        <v>1.352</v>
+        <v>-0.4477</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6879</v>
+        <v>-0.8212</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.438</v>
+        <v>-0.9688</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.1591</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8095</v>
+        <v>-0.8097</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7995</v>
+        <v>0.7208</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4237</v>
+        <v>0.0497</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3759</v>
+        <v>0.6712</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2186</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.75</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.991</v>
+        <v>1.5701</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2411</v>
+        <v>-2.1735</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2377</v>
+        <v>2.4767</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6068</v>
+        <v>1.8565</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6309</v>
+        <v>0.6202</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2689</v>
+        <v>2.5611</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4477</v>
+        <v>2.4802</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8212</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9688</v>
+        <v>-0.0844</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1591</v>
+        <v>-0.6237</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8097</v>
+        <v>0.5393</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5343</v>
+        <v>0.7126</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3548</v>
+        <v>0.3179</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8891</v>
+        <v>0.3948</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6093</v>
+        <v>-3.988</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6093</v>
+        <v>-0.3321</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>-3.6559</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9842</v>
+        <v>-1.2871</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3488</v>
+        <v>-3.0403</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.333</v>
+        <v>1.7532</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8459</v>
+        <v>-2.4812</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5224</v>
+        <v>0.8089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3235</v>
+        <v>-3.2902</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4283</v>
+        <v>-1.7968</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6999</v>
+        <v>0.8186</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7284</v>
+        <v>-2.6155</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5824</v>
+        <v>-0.6844</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1775</v>
+        <v>-0.0097</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4049</v>
+        <v>-0.6747</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8341</v>
+        <v>0.7216</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5381</v>
+        <v>0.4327</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2959</v>
+        <v>0.2888</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4921</v>
+        <v>0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8083</v>
+        <v>-1.6799</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3436</v>
+        <v>0.7621</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5353</v>
+        <v>-2.442</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4812</v>
+        <v>0.8459</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8089</v>
+        <v>0.5224</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.2902</v>
+        <v>0.3235</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7968</v>
+        <v>2.4283</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8186</v>
+        <v>1.6999</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6155</v>
+        <v>0.7284</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6844</v>
+        <v>-1.5824</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0097</v>
+        <v>-1.1775</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6747</v>
+        <v>-0.4049</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2004</v>
+        <v>1.1384</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1294</v>
+        <v>0.9514</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.187</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2772</v>
+        <v>-2.4921</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.0877</v>
+        <v>15.693</v>
       </c>
       <c r="E14" t="n">
-        <v>8.410000000000002</v>
+        <v>9.015099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>6.677800000000002</v>
+        <v>6.677699999999998</v>
       </c>
       <c r="G14" t="n">
         <v>11.9303</v>
@@ -1525,7 +1525,7 @@
         <v>15.495</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0291</v>
+        <v>2.029100000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-5.5939</v>
@@ -1537,7 +1537,7 @@
         <v>-6.747999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0002000000000001168</v>
+        <v>-0.0002000000000002</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.5807</v>
@@ -1546,16 +1546,16 @@
         <v>17.581</v>
       </c>
       <c r="S14" t="n">
-        <v>8.4192</v>
+        <v>9.0242</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7565</v>
+        <v>4.3619</v>
       </c>
       <c r="U14" t="n">
-        <v>4.662399999999999</v>
+        <v>4.6623</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.261500000000001</v>
+        <v>-5.2615</v>
       </c>
       <c r="W14" t="n">
         <v>4.7098</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2222</v>
+        <v>0.2767</v>
       </c>
       <c r="E15" t="n">
         <v>0.3751</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1529</v>
+        <v>-0.0984</v>
       </c>
       <c r="G15" t="n">
         <v>1.6392</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5222</v>
+        <v>-0.4677</v>
       </c>
       <c r="T15" t="n">
         <v>-0.2805</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2417</v>
+        <v>-0.1872</v>
       </c>
       <c r="V15" t="n">
         <v>0.2772</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1111</v>
+        <v>-0.148</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7362</v>
+        <v>1.9231</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-2.0711</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5413</v>
+        <v>1.2416</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0663</v>
+        <v>-0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6076</v>
+        <v>1.3212</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7206</v>
+        <v>3.094</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5183</v>
+        <v>1.6373</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2023</v>
+        <v>1.4568</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2619</v>
+        <v>-1.8524</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.452</v>
+        <v>-1.7168</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8099</v>
+        <v>-0.1356</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7814</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>-3.1255</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8601</v>
+        <v>-0.6864</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1594</v>
+        <v>-0.4827</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7006</v>
+        <v>-0.2037</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0717</v>
+        <v>0.6642</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1052</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0335</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2726</v>
+        <v>-0.3405</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1253</v>
+        <v>0.534</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3979</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2416</v>
+        <v>-0.5413</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0795</v>
+        <v>0.0663</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3212</v>
+        <v>-0.6076</v>
       </c>
       <c r="J17" t="n">
-        <v>3.094</v>
+        <v>1.7206</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6373</v>
+        <v>1.5183</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4568</v>
+        <v>0.2023</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8524</v>
+        <v>-2.2619</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7168</v>
+        <v>-1.452</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1356</v>
+        <v>-0.8099</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1255</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2805</v>
+        <v>-0.3617</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5305</v>
+        <v>-0.7278</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6642</v>
+        <v>2.0717</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4373</v>
+        <v>2.1052</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7731</v>
+        <v>-0.0335</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7628</v>
+        <v>-0.8894</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0265</v>
+        <v>-0.4095</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7363</v>
+        <v>-0.4799</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2359</v>
+        <v>-2.547</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.0699</v>
+        <v>-3.5186</v>
       </c>
       <c r="I18" t="n">
-        <v>1.834</v>
+        <v>0.9716</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8497</v>
+        <v>-1.1645</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7944</v>
+        <v>-1.732</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6441</v>
+        <v>0.5675</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0856</v>
+        <v>-1.3826</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.2755</v>
+        <v>-1.7866</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8101</v>
+        <v>0.4041</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4468</v>
+        <v>-0.8047</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.5103</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2573</v>
+        <v>-0.2945</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6428</v>
+        <v>2.0717</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6428</v>
+        <v>-0.3656</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.965</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2857</v>
+        <v>0.0746</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2507</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4215</v>
+        <v>-1.2359</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7488</v>
+        <v>-3.0699</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6727</v>
+        <v>1.834</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3943</v>
+        <v>1.8497</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6615</v>
+        <v>-0.7944</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2673</v>
+        <v>2.6441</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8158</v>
+        <v>-3.0856</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4103</v>
+        <v>-2.2755</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4054</v>
+        <v>-0.8101</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="Q19" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.5908</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.603</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.6428</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.3441</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.1314</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.7179</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.4134</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.2437</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.6093</v>
-      </c>
       <c r="X19" t="n">
-        <v>-0.3656</v>
+        <v>-0.6428</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.364</v>
+        <v>-1.1557</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6118</v>
+        <v>0.2857</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7523</v>
+        <v>-1.4413</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.547</v>
+        <v>-2.4215</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.5186</v>
+        <v>-0.7488</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9716</v>
+        <v>-1.6727</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1645</v>
+        <v>0.3943</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.732</v>
+        <v>1.6615</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5675</v>
+        <v>-1.2673</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3826</v>
+        <v>-2.8158</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7866</v>
+        <v>-2.4103</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4041</v>
+        <v>-0.4054</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2793</v>
+        <v>-1.322</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7125</v>
+        <v>-0.7179</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5668</v>
+        <v>-0.6041</v>
       </c>
       <c r="V20" t="n">
-        <v>2.0717</v>
+        <v>0.2437</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4373</v>
+        <v>0.6093</v>
       </c>
       <c r="X20" t="n">
         <v>-0.3656</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1635</v>
+        <v>-2.2996</v>
       </c>
       <c r="E21" t="n">
         <v>-2.2142</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0508</v>
+        <v>-0.0854</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2519</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6576</v>
+        <v>-0.7938</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3631</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2945</v>
+        <v>-0.4307</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2772</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4053</v>
+        <v>-2.4948</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8292</v>
+        <v>-0.728</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5761</v>
+        <v>-1.7668</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0571</v>
@@ -2170,13 +2170,13 @@
         <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5453</v>
+        <v>-0.6349</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5447</v>
+        <v>-0.4436</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.1913</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9749</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2656</v>
+        <v>-7.1295</v>
       </c>
       <c r="E23" t="n">
         <v>-6.5185</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7471</v>
+        <v>-0.611</v>
       </c>
       <c r="G23" t="n">
         <v>-5.7563</v>
@@ -2248,13 +2248,13 @@
         <v>2.9301</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1653</v>
+        <v>-2.0291</v>
       </c>
       <c r="T23" t="n">
         <v>-0.8995</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2658</v>
+        <v>-1.1296</v>
       </c>
       <c r="V23" t="n">
         <v>1.8279</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.0877</v>
+        <v>-15.0876</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6779</v>
+        <v>-6.6777</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.409799999999999</v>
+        <v>-8.409800000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-11.9302</v>
@@ -2299,7 +2299,7 @@
         <v>4.7188</v>
       </c>
       <c r="J24" t="n">
-        <v>5.593799999999997</v>
+        <v>5.593799999999999</v>
       </c>
       <c r="K24" t="n">
         <v>-1.1541</v>
@@ -2317,7 +2317,7 @@
         <v>-2.0291</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q24" t="n">
         <v>-17.5809</v>
@@ -2326,13 +2326,13 @@
         <v>17.5808</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.419</v>
+        <v>-8.418900000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.662199999999999</v>
+        <v>-4.6623</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.7566</v>
+        <v>-3.7567</v>
       </c>
       <c r="V24" t="n">
         <v>5.2615</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484207_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484207_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,28 +653,28 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.821</v>
+        <v>4.514</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1253</v>
+        <v>2.8183</v>
       </c>
       <c r="F3" t="n">
         <v>1.6957</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2757</v>
+        <v>1.9687</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5337</v>
+        <v>1.2267</v>
       </c>
       <c r="I3" t="n">
         <v>0.742</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4307</v>
+        <v>2.1237</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1486</v>
+        <v>0.8416</v>
       </c>
       <c r="L3" t="n">
         <v>1.2821</v>
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -799,67 +819,72 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5754</v>
+        <v>2.1419</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2059</v>
+        <v>2.1419</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7813</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6212</v>
+        <v>2.1419</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0663</v>
+        <v>1.5349</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4451</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6363</v>
+        <v>2.1419</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5416</v>
+        <v>1.5349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0152</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5247000000000001</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.7115</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4471</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8227</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +985,72 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0173</v>
+        <v>0.914</v>
       </c>
       <c r="E7" t="n">
-        <v>1.423</v>
+        <v>0.914</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4057</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8475</v>
+        <v>0.914</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2676</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5799</v>
+        <v>0.607</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2573</v>
+        <v>0.914</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0028</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2544</v>
+        <v>0.607</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4097</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2648</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1149</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1424</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0275</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1095,11 +1130,16 @@
       <c r="X8" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0259</v>
+        <v>0.7103</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9801</v>
+        <v>1.116</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0061</v>
+        <v>-0.4057</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6019</v>
+        <v>1.5406</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7235</v>
+        <v>0.9606</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1216</v>
+        <v>0.5799</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0399</v>
+        <v>1.9503</v>
       </c>
       <c r="K9" t="n">
-        <v>1.352</v>
+        <v>0.6958</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6879</v>
+        <v>1.2544</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.438</v>
+        <v>-0.4097</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.2648</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8095</v>
+        <v>-0.6745</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1905</v>
+        <v>0.1149</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0598</v>
+        <v>0.1424</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1308</v>
+        <v>-0.0275</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5634</v>
+        <v>0.307</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5866</v>
+        <v>0.307</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0232</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2377</v>
+        <v>0.307</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6068</v>
+        <v>0.307</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6309</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2689</v>
+        <v>0.307</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4477</v>
+        <v>0.307</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8212</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9688</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1591</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8097</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7208</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0497</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6712</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6032999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5701</v>
+        <v>0.307</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1735</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4767</v>
+        <v>0.307</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8565</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6202</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5611</v>
+        <v>0.307</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4802</v>
+        <v>0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0844</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6237</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5393</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7126</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3179</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3948</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.988</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.6559</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2871</v>
+        <v>-0.5634</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0403</v>
+        <v>-1.5866</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7532</v>
+        <v>1.0232</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4812</v>
+        <v>-2.2377</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8089</v>
+        <v>-0.6068</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.2902</v>
+        <v>-1.6309</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7968</v>
+        <v>-1.2689</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8186</v>
+        <v>-0.4477</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6155</v>
+        <v>-0.8212</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6844</v>
+        <v>-0.9688</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0097</v>
+        <v>-0.1591</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6747</v>
+        <v>-0.8097</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7216</v>
+        <v>0.7208</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4327</v>
+        <v>0.0497</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2888</v>
+        <v>0.6712</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6799</v>
+        <v>-0.5665</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7621</v>
+        <v>-2.3479</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.442</v>
+        <v>1.7813</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8459</v>
+        <v>0.4792</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5224</v>
+        <v>1.5313</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3235</v>
+        <v>-1.0521</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4283</v>
+        <v>0.4944</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6999</v>
+        <v>1.0066</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7284</v>
+        <v>-0.5122</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5824</v>
+        <v>-0.0152</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1775</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4049</v>
+        <v>-0.5399</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1721</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-4.8836</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1384</v>
+        <v>1.4471</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9514</v>
+        <v>0.8227</v>
       </c>
       <c r="U13" t="n">
-        <v>0.187</v>
+        <v>0.6244</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.4921</v>
+        <v>1.2186</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,385 +1566,406 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.693</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>9.015099999999999</v>
+        <v>1.5701</v>
       </c>
       <c r="F14" t="n">
-        <v>6.677699999999998</v>
+        <v>-2.1735</v>
       </c>
       <c r="G14" t="n">
-        <v>11.9303</v>
+        <v>2.4767</v>
       </c>
       <c r="H14" t="n">
-        <v>16.6491</v>
+        <v>1.8565</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.7188</v>
+        <v>0.6202</v>
       </c>
       <c r="J14" t="n">
-        <v>17.5241</v>
+        <v>2.5611</v>
       </c>
       <c r="K14" t="n">
-        <v>15.495</v>
+        <v>2.4802</v>
       </c>
       <c r="L14" t="n">
-        <v>2.029100000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.5939</v>
+        <v>-0.0844</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1539</v>
+        <v>-0.6237</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.747999999999999</v>
+        <v>0.5393</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0002000000000002</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.5807</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>17.581</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>9.0242</v>
+        <v>0.7126</v>
       </c>
       <c r="T14" t="n">
-        <v>4.3619</v>
+        <v>0.3179</v>
       </c>
       <c r="U14" t="n">
-        <v>4.6623</v>
+        <v>0.3948</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.2615</v>
+        <v>-3.988</v>
       </c>
       <c r="W14" t="n">
-        <v>4.7098</v>
+        <v>-0.3321</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.971299999999999</v>
+        <v>-3.6559</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2767</v>
+        <v>-0.9399</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3751</v>
+        <v>1.0662</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0984</v>
+        <v>-2.0061</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6392</v>
+        <v>-0.3121</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3126</v>
+        <v>0.4165</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9518</v>
+        <v>-0.7286</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2266</v>
+        <v>1.126</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.591</v>
+        <v>1.045</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8176</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5874</v>
+        <v>-1.438</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7217</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1342</v>
+        <v>-0.8095</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4677</v>
+        <v>-0.1905</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2805</v>
+        <v>-0.0598</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1872</v>
+        <v>-0.1308</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.148</v>
+        <v>-1.2871</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9231</v>
+        <v>-3.0403</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0711</v>
+        <v>1.7532</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2416</v>
+        <v>-2.4812</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0795</v>
+        <v>0.8089</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3212</v>
+        <v>-3.2902</v>
       </c>
       <c r="J16" t="n">
-        <v>3.094</v>
+        <v>-1.7968</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6373</v>
+        <v>0.8186</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4568</v>
+        <v>-2.6155</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8524</v>
+        <v>-0.6844</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7168</v>
+        <v>-0.0097</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1356</v>
+        <v>-0.6747</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6864</v>
+        <v>0.7216</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4827</v>
+        <v>0.4327</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2037</v>
+        <v>0.2888</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3405</v>
+        <v>-1.6799</v>
       </c>
       <c r="E17" t="n">
-        <v>0.534</v>
+        <v>0.7621</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-2.442</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5413</v>
+        <v>0.8459</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0663</v>
+        <v>0.5224</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6076</v>
+        <v>0.3235</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7206</v>
+        <v>2.4283</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5183</v>
+        <v>1.6999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2023</v>
+        <v>0.7284</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2619</v>
+        <v>-1.5824</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.452</v>
+        <v>-1.1775</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8099</v>
+        <v>-0.4049</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0895</v>
+        <v>1.1384</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3617</v>
+        <v>0.9514</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7278</v>
+        <v>0.187</v>
       </c>
       <c r="V17" t="n">
-        <v>2.0717</v>
+        <v>-2.4921</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1052</v>
+        <v>-0.6642</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0335</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8894</v>
+        <v>15.693</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4095</v>
+        <v>9.0151</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4799</v>
+        <v>6.6777</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.547</v>
+        <v>11.9303</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.5186</v>
+        <v>16.649</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9716</v>
+        <v>-4.7188</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1645</v>
+        <v>17.5242</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.732</v>
+        <v>15.4949</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5675</v>
+        <v>2.0292</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3826</v>
+        <v>-5.5939</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7866</v>
+        <v>1.1539</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4041</v>
+        <v>-6.747999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>-0.0002000000000002</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>-17.5807</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>17.581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8047</v>
+        <v>9.0242</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5103</v>
+        <v>4.3619</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2945</v>
+        <v>4.6623</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0717</v>
+        <v>-5.2615</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4373</v>
+        <v>4.7098</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3656</v>
-      </c>
+        <v>-9.971299999999999</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9068000000000001</v>
+        <v>0.2767</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0746</v>
+        <v>0.3751</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.0984</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2359</v>
+        <v>1.6392</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.0699</v>
+        <v>-2.3126</v>
       </c>
       <c r="I19" t="n">
-        <v>1.834</v>
+        <v>3.9518</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8497</v>
+        <v>3.2266</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7944</v>
+        <v>-0.591</v>
       </c>
       <c r="L19" t="n">
-        <v>2.6441</v>
+        <v>3.8176</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0856</v>
+        <v>-1.5874</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.2755</v>
+        <v>-1.7217</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8101</v>
+        <v>0.1342</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5627</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-3.1255</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7348</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5908</v>
+        <v>-0.4677</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.603</v>
+        <v>-0.2805</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0122</v>
+        <v>-0.1872</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6428</v>
+        <v>0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6428</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1557</v>
+        <v>-0.148</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2857</v>
+        <v>1.9231</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4413</v>
+        <v>-2.0711</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4215</v>
+        <v>1.2416</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7488</v>
+        <v>-0.0795</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6727</v>
+        <v>1.3212</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3943</v>
+        <v>3.094</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6615</v>
+        <v>1.6373</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2673</v>
+        <v>1.4568</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8158</v>
+        <v>-1.8524</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4103</v>
+        <v>-1.7168</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4054</v>
+        <v>-0.1356</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3441</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.322</v>
+        <v>-0.6864</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7179</v>
+        <v>-0.4827</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6041</v>
+        <v>-0.2037</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2437</v>
+        <v>0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6093</v>
+        <v>2.4373</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3656</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BALLO RODRIGUEZ</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2996</v>
+        <v>-0.3405</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2142</v>
+        <v>0.534</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0854</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2519</v>
+        <v>-0.5413</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.791</v>
+        <v>0.0663</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5391</v>
+        <v>-0.6076</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1023</v>
+        <v>1.7206</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1023</v>
+        <v>1.5183</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.2023</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3542</v>
+        <v>-2.2619</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8933</v>
+        <v>-1.452</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5391</v>
+        <v>-0.8099</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7938</v>
+        <v>-1.0895</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3631</v>
+        <v>-0.3617</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4307</v>
+        <v>-0.7278</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>2.0717</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-0.0335</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4948</v>
+        <v>-0.8894</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.728</v>
+        <v>-0.4095</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7668</v>
+        <v>-0.4799</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0571</v>
+        <v>-2.547</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2881</v>
+        <v>-3.5186</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.769</v>
+        <v>0.9716</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2844</v>
+        <v>-1.1645</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3249</v>
+        <v>-1.732</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>0.5675</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7727</v>
+        <v>-1.3826</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.7866</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8095</v>
+        <v>0.4041</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6349</v>
+        <v>-0.8047</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4436</v>
+        <v>-0.5103</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1913</v>
+        <v>-0.2945</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9749</v>
+        <v>2.0717</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9749</v>
+        <v>-0.3656</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1295</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.5185</v>
+        <v>0.0746</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.611</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.7563</v>
+        <v>-1.2359</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.9067</v>
+        <v>-3.0699</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8496</v>
+        <v>1.834</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.3448</v>
+        <v>1.8497</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.6312</v>
+        <v>-0.7944</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7136</v>
+        <v>2.6441</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4115</v>
+        <v>-3.0856</v>
       </c>
       <c r="N23" t="n">
         <v>-2.2755</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.136</v>
+        <v>-0.8101</v>
       </c>
       <c r="P23" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-4.1022</v>
-      </c>
       <c r="R23" t="n">
-        <v>2.9301</v>
+        <v>2.7348</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0291</v>
+        <v>-0.5908</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8995</v>
+        <v>-0.603</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1296</v>
+        <v>0.0122</v>
       </c>
       <c r="V23" t="n">
-        <v>1.8279</v>
+        <v>-0.6428</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.6428</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,401 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-1.1557</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.4413</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.4215</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.7488</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.6727</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.6615</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.2673</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.8158</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-2.4103</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.4054</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-1.322</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.7179</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.6041</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.3656</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>D. BALLO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.2996</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.2142</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.0854</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.2519</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.791</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.3542</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.8933</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.7938</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.3631</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.4307</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>J. CALLAVE FERRER</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.4948</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.728</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.7668</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.0571</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.2881</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.769</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.2844</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.3249</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.7727</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.9631999999999999</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.8095</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.6349</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.4436</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.1913</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.9749</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.9749</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R. GUARDIOLA DISPES</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-7.1295</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-6.5185</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.611</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-5.7563</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-4.9067</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.8496</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-3.3448</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-2.6312</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.7136</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-2.4115</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-2.2755</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-4.1022</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-2.0291</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.8995</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-1.1296</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.8279</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.8279</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484207_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>-15.0876</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E28" t="n">
         <v>-6.6777</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F28" t="n">
         <v>-8.409800000000001</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G28" t="n">
         <v>-11.9302</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H28" t="n">
         <v>-16.6489</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I28" t="n">
         <v>4.7188</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J28" t="n">
         <v>5.593799999999999</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K28" t="n">
         <v>-1.1541</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L28" t="n">
         <v>6.7479</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M28" t="n">
         <v>-17.5241</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N28" t="n">
         <v>-15.4949</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O28" t="n">
         <v>-2.0291</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P28" t="n">
         <v>-9.999999999976694e-05</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q28" t="n">
         <v>-17.5809</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R28" t="n">
         <v>17.5808</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S28" t="n">
         <v>-8.418900000000001</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T28" t="n">
         <v>-4.6623</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U28" t="n">
         <v>-3.7567</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V28" t="n">
         <v>5.2615</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W28" t="n">
         <v>9.971499999999999</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X28" t="n">
         <v>-4.709899999999999</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
